--- a/SAP/CONTRATOS/Planilhas/Contratos.xlsx
+++ b/SAP/CONTRATOS/Planilhas/Contratos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junio\OneDrive\Área de Trabalho\Documentos\Scripts Github\automations\SAP\CONTRATOS\Planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_scripts\SAP\CONTRATOS\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A829D494-46C6-4F4E-8A2E-ACFA8D5EFEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFF1E09-CEE5-4F07-B33F-8066B1CFD0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C88C6739-E8C1-4ABA-A295-F3266F31B792}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{C88C6739-E8C1-4ABA-A295-F3266F31B792}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
   <si>
     <t>ID_CONTRATO</t>
   </si>
@@ -81,53 +81,35 @@
     <t>MK</t>
   </si>
   <si>
-    <t>31.12.2024</t>
-  </si>
-  <si>
     <t>CIF</t>
   </si>
   <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>50.00</t>
-  </si>
-  <si>
-    <t>I1</t>
-  </si>
-  <si>
     <t>BRL</t>
   </si>
   <si>
-    <t>15.50</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>WK</t>
-  </si>
-  <si>
-    <t>30.06.2025</t>
-  </si>
-  <si>
-    <t>FOB</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro</t>
-  </si>
-  <si>
-    <t>120.00</t>
-  </si>
-  <si>
-    <t>I0</t>
+    <t>MI01</t>
+  </si>
+  <si>
+    <t>I14</t>
+  </si>
+  <si>
+    <t>31.10.2026</t>
+  </si>
+  <si>
+    <t>P080</t>
+  </si>
+  <si>
+    <t>MATRIZ</t>
+  </si>
+  <si>
+    <t>C8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,17 +118,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -181,19 +171,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -210,9 +201,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -250,7 +241,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -356,7 +347,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -498,7 +489,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -507,26 +498,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B4A2AF-DF9C-4A3E-801E-187E389FE683}">
   <dimension ref="A1:Q4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,161 +572,160 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>100500</v>
+        <v>1030687</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="3">
+        <v>20000991</v>
+      </c>
+      <c r="L2" s="2">
         <v>1000</v>
       </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1100</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="1">
-        <v>99001</v>
-      </c>
-      <c r="L2" s="2">
-        <v>100</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>21</v>
+      <c r="M2" s="2">
+        <v>2.52</v>
       </c>
       <c r="N2" s="2">
         <v>1</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>100500</v>
+        <v>1030687</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3">
+        <v>20001626</v>
+      </c>
+      <c r="L3" s="2">
         <v>1000</v>
       </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1100</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="1">
-        <v>99002</v>
-      </c>
-      <c r="L3" s="2">
-        <v>300</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>24</v>
+      <c r="M3" s="2">
+        <v>1.1100000000000001</v>
       </c>
       <c r="N3" s="2">
         <v>1</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="2"/>
+      <c r="P3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="Q3" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>200300</v>
+        <v>1030687</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2000</v>
-      </c>
-      <c r="E4" s="2">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="2">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3">
+        <v>20001627</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="2">
         <v>2</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="1">
-        <v>88005</v>
-      </c>
-      <c r="L4" s="2">
-        <v>50</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="N4" s="2">
         <v>1</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1" display="https://s4qas.sap.avivar.com.br/sap/bc/ui2/flp?sap-client=300&amp;sap-language=PT" xr:uid="{4B98B7FC-1CC0-4D3C-B6BF-3C6E87028F70}"/>
+    <hyperlink ref="K3" r:id="rId2" display="https://s4qas.sap.avivar.com.br/sap/bc/ui2/flp?sap-client=300&amp;sap-language=PT" xr:uid="{2A0D511D-07A5-45D3-B358-F3A5049F9C37}"/>
+    <hyperlink ref="K4" r:id="rId3" display="https://s4qas.sap.avivar.com.br/sap/bc/ui2/flp?sap-client=300&amp;sap-language=PT" xr:uid="{8BD7C034-9356-45C8-B16D-B99C4C4C76DD}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/SAP/CONTRATOS/Planilhas/Contratos.xlsx
+++ b/SAP/CONTRATOS/Planilhas/Contratos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junio\OneDrive\Área de Trabalho\Documentos\Scripts Github\automations\SAP\CONTRATOS\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A829D494-46C6-4F4E-8A2E-ACFA8D5EFEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0FE43D-046F-4BCF-81A4-2F991CE2F150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C88C6739-E8C1-4ABA-A295-F3266F31B792}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>ID_CONTRATO</t>
   </si>
@@ -72,62 +72,38 @@
     <t>Classificação Contabil</t>
   </si>
   <si>
-    <t>Cód. Imposto</t>
-  </si>
-  <si>
     <t>Moeda</t>
   </si>
   <si>
     <t>MK</t>
   </si>
   <si>
-    <t>31.12.2024</t>
-  </si>
-  <si>
     <t>CIF</t>
   </si>
   <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>50.00</t>
-  </si>
-  <si>
-    <t>I1</t>
-  </si>
-  <si>
     <t>BRL</t>
   </si>
   <si>
-    <t>15.50</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>WK</t>
-  </si>
-  <si>
-    <t>30.06.2025</t>
-  </si>
-  <si>
-    <t>FOB</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro</t>
-  </si>
-  <si>
-    <t>120.00</t>
-  </si>
-  <si>
-    <t>I0</t>
+    <t>MI01</t>
+  </si>
+  <si>
+    <t>I14</t>
+  </si>
+  <si>
+    <t>31.10.2026</t>
+  </si>
+  <si>
+    <t>P080</t>
+  </si>
+  <si>
+    <t>MATRIZ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,17 +112,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -181,19 +165,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -506,27 +491,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B4A2AF-DF9C-4A3E-801E-187E389FE683}">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -575,165 +561,152 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>100500</v>
+        <v>1030687</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2">
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="3">
+        <v>20000991</v>
+      </c>
+      <c r="L2" s="2">
         <v>1000</v>
       </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1100</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="1">
-        <v>99001</v>
-      </c>
-      <c r="L2" s="2">
-        <v>100</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>21</v>
+      <c r="M2" s="2">
+        <v>2.52</v>
       </c>
       <c r="N2" s="2">
         <v>1</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>100500</v>
+        <v>1030687</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2">
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="3">
+        <v>20001626</v>
+      </c>
+      <c r="L3" s="2">
         <v>1000</v>
       </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1100</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="1">
-        <v>99002</v>
-      </c>
-      <c r="L3" s="2">
-        <v>300</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>24</v>
+      <c r="M3" s="2">
+        <v>1.1100000000000001</v>
       </c>
       <c r="N3" s="2">
         <v>1</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>200300</v>
+        <v>1030687</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2000</v>
-      </c>
-      <c r="E4" s="2">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="2">
+        <v>21</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="3">
+        <v>20001627</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="2">
         <v>2</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="1">
-        <v>88005</v>
-      </c>
-      <c r="L4" s="2">
-        <v>50</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="N4" s="2">
         <v>1</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1" display="https://s4qas.sap.avivar.com.br/sap/bc/ui2/flp?sap-client=300&amp;sap-language=PT" xr:uid="{4B98B7FC-1CC0-4D3C-B6BF-3C6E87028F70}"/>
+    <hyperlink ref="K3" r:id="rId2" display="https://s4qas.sap.avivar.com.br/sap/bc/ui2/flp?sap-client=300&amp;sap-language=PT" xr:uid="{2A0D511D-07A5-45D3-B358-F3A5049F9C37}"/>
+    <hyperlink ref="K4" r:id="rId3" display="https://s4qas.sap.avivar.com.br/sap/bc/ui2/flp?sap-client=300&amp;sap-language=PT" xr:uid="{8BD7C034-9356-45C8-B16D-B99C4C4C76DD}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/SAP/CONTRATOS/Planilhas/Contratos.xlsx
+++ b/SAP/CONTRATOS/Planilhas/Contratos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_scripts\SAP\CONTRATOS\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D0CC09-7EB4-41B2-8178-4B27FF18A912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69071017-53D4-46AD-BE43-DD4751A8A5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{C88C6739-E8C1-4ABA-A295-F3266F31B792}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{C88C6739-E8C1-4ABA-A295-F3266F31B792}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="26">
   <si>
     <t>ID_CONTRATO</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>C1</t>
+  </si>
+  <si>
+    <t>U</t>
   </si>
 </sst>
 </file>
@@ -566,9 +569,6 @@
       <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>2001</v>
-      </c>
       <c r="G2" t="s">
         <v>21</v>
       </c>
@@ -593,6 +593,9 @@
       <c r="N2">
         <v>100</v>
       </c>
+      <c r="O2" t="s">
+        <v>25</v>
+      </c>
       <c r="P2" t="s">
         <v>24</v>
       </c>
@@ -616,9 +619,6 @@
       <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="F3">
-        <v>2001</v>
-      </c>
       <c r="G3" t="s">
         <v>21</v>
       </c>
@@ -666,9 +666,6 @@
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4">
-        <v>2001</v>
-      </c>
       <c r="G4" t="s">
         <v>21</v>
       </c>
@@ -716,9 +713,6 @@
       <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="F5">
-        <v>2001</v>
-      </c>
       <c r="G5" t="s">
         <v>21</v>
       </c>
@@ -766,9 +760,6 @@
       <c r="E6" t="s">
         <v>20</v>
       </c>
-      <c r="F6">
-        <v>2001</v>
-      </c>
       <c r="G6" t="s">
         <v>21</v>
       </c>
@@ -816,9 +807,6 @@
       <c r="E7" t="s">
         <v>20</v>
       </c>
-      <c r="F7">
-        <v>2001</v>
-      </c>
       <c r="G7" t="s">
         <v>21</v>
       </c>
@@ -866,9 +854,6 @@
       <c r="E8" t="s">
         <v>20</v>
       </c>
-      <c r="F8">
-        <v>2001</v>
-      </c>
       <c r="G8" t="s">
         <v>21</v>
       </c>
@@ -916,9 +901,6 @@
       <c r="E9" t="s">
         <v>20</v>
       </c>
-      <c r="F9">
-        <v>2001</v>
-      </c>
       <c r="G9" t="s">
         <v>21</v>
       </c>
@@ -966,9 +948,6 @@
       <c r="E10" t="s">
         <v>20</v>
       </c>
-      <c r="F10">
-        <v>2001</v>
-      </c>
       <c r="G10" t="s">
         <v>21</v>
       </c>
@@ -1016,9 +995,6 @@
       <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="F11">
-        <v>2001</v>
-      </c>
       <c r="G11" t="s">
         <v>21</v>
       </c>
@@ -1066,9 +1042,6 @@
       <c r="E12" t="s">
         <v>20</v>
       </c>
-      <c r="F12">
-        <v>2001</v>
-      </c>
       <c r="G12" t="s">
         <v>21</v>
       </c>
@@ -1116,9 +1089,6 @@
       <c r="E13" t="s">
         <v>20</v>
       </c>
-      <c r="F13">
-        <v>2001</v>
-      </c>
       <c r="G13" t="s">
         <v>21</v>
       </c>
@@ -1166,9 +1136,6 @@
       <c r="E14" t="s">
         <v>20</v>
       </c>
-      <c r="F14">
-        <v>2001</v>
-      </c>
       <c r="G14" t="s">
         <v>21</v>
       </c>
@@ -1216,9 +1183,6 @@
       <c r="E15" t="s">
         <v>20</v>
       </c>
-      <c r="F15">
-        <v>2001</v>
-      </c>
       <c r="G15" t="s">
         <v>21</v>
       </c>
@@ -1266,9 +1230,6 @@
       <c r="E16" t="s">
         <v>20</v>
       </c>
-      <c r="F16">
-        <v>2001</v>
-      </c>
       <c r="G16" t="s">
         <v>21</v>
       </c>
@@ -1316,9 +1277,6 @@
       <c r="E17" t="s">
         <v>20</v>
       </c>
-      <c r="F17">
-        <v>2001</v>
-      </c>
       <c r="G17" t="s">
         <v>21</v>
       </c>
@@ -1366,9 +1324,6 @@
       <c r="E18" t="s">
         <v>20</v>
       </c>
-      <c r="F18">
-        <v>2001</v>
-      </c>
       <c r="G18" t="s">
         <v>21</v>
       </c>
@@ -1416,9 +1371,6 @@
       <c r="E19" t="s">
         <v>20</v>
       </c>
-      <c r="F19">
-        <v>2001</v>
-      </c>
       <c r="G19" t="s">
         <v>21</v>
       </c>
@@ -1466,9 +1418,6 @@
       <c r="E20" t="s">
         <v>20</v>
       </c>
-      <c r="F20">
-        <v>2001</v>
-      </c>
       <c r="G20" t="s">
         <v>21</v>
       </c>
@@ -1516,9 +1465,6 @@
       <c r="E21" t="s">
         <v>20</v>
       </c>
-      <c r="F21">
-        <v>2001</v>
-      </c>
       <c r="G21" t="s">
         <v>21</v>
       </c>
@@ -1566,9 +1512,6 @@
       <c r="E22" t="s">
         <v>20</v>
       </c>
-      <c r="F22">
-        <v>2001</v>
-      </c>
       <c r="G22" t="s">
         <v>21</v>
       </c>
@@ -1616,9 +1559,6 @@
       <c r="E23" t="s">
         <v>20</v>
       </c>
-      <c r="F23">
-        <v>2001</v>
-      </c>
       <c r="G23" t="s">
         <v>21</v>
       </c>
@@ -1666,9 +1606,6 @@
       <c r="E24" t="s">
         <v>20</v>
       </c>
-      <c r="F24">
-        <v>2001</v>
-      </c>
       <c r="G24" t="s">
         <v>21</v>
       </c>
@@ -1716,9 +1653,6 @@
       <c r="E25" t="s">
         <v>20</v>
       </c>
-      <c r="F25">
-        <v>2001</v>
-      </c>
       <c r="G25" t="s">
         <v>21</v>
       </c>
@@ -1766,9 +1700,6 @@
       <c r="E26" t="s">
         <v>20</v>
       </c>
-      <c r="F26">
-        <v>2001</v>
-      </c>
       <c r="G26" t="s">
         <v>21</v>
       </c>
@@ -1816,9 +1747,6 @@
       <c r="E27" t="s">
         <v>20</v>
       </c>
-      <c r="F27">
-        <v>2001</v>
-      </c>
       <c r="G27" t="s">
         <v>21</v>
       </c>
@@ -1866,9 +1794,6 @@
       <c r="E28" t="s">
         <v>20</v>
       </c>
-      <c r="F28">
-        <v>2001</v>
-      </c>
       <c r="G28" t="s">
         <v>21</v>
       </c>
@@ -1916,9 +1841,6 @@
       <c r="E29" t="s">
         <v>20</v>
       </c>
-      <c r="F29">
-        <v>2001</v>
-      </c>
       <c r="G29" t="s">
         <v>21</v>
       </c>
@@ -1966,9 +1888,6 @@
       <c r="E30" t="s">
         <v>20</v>
       </c>
-      <c r="F30">
-        <v>2001</v>
-      </c>
       <c r="G30" t="s">
         <v>21</v>
       </c>
@@ -2016,9 +1935,6 @@
       <c r="E31" t="s">
         <v>20</v>
       </c>
-      <c r="F31">
-        <v>2001</v>
-      </c>
       <c r="G31" t="s">
         <v>21</v>
       </c>
@@ -2066,9 +1982,6 @@
       <c r="E32" t="s">
         <v>20</v>
       </c>
-      <c r="F32">
-        <v>2001</v>
-      </c>
       <c r="G32" t="s">
         <v>21</v>
       </c>
@@ -2116,9 +2029,6 @@
       <c r="E33" t="s">
         <v>20</v>
       </c>
-      <c r="F33">
-        <v>2001</v>
-      </c>
       <c r="G33" t="s">
         <v>21</v>
       </c>
@@ -2166,9 +2076,6 @@
       <c r="E34" t="s">
         <v>20</v>
       </c>
-      <c r="F34">
-        <v>2001</v>
-      </c>
       <c r="G34" t="s">
         <v>21</v>
       </c>
@@ -2216,9 +2123,6 @@
       <c r="E35" t="s">
         <v>20</v>
       </c>
-      <c r="F35">
-        <v>2001</v>
-      </c>
       <c r="G35" t="s">
         <v>21</v>
       </c>
@@ -2266,9 +2170,6 @@
       <c r="E36" t="s">
         <v>20</v>
       </c>
-      <c r="F36">
-        <v>2001</v>
-      </c>
       <c r="G36" t="s">
         <v>21</v>
       </c>
@@ -2316,9 +2217,6 @@
       <c r="E37" t="s">
         <v>20</v>
       </c>
-      <c r="F37">
-        <v>2001</v>
-      </c>
       <c r="G37" t="s">
         <v>21</v>
       </c>
@@ -2366,9 +2264,6 @@
       <c r="E38" t="s">
         <v>20</v>
       </c>
-      <c r="F38">
-        <v>2001</v>
-      </c>
       <c r="G38" t="s">
         <v>21</v>
       </c>
@@ -2416,9 +2311,6 @@
       <c r="E39" t="s">
         <v>20</v>
       </c>
-      <c r="F39">
-        <v>2001</v>
-      </c>
       <c r="G39" t="s">
         <v>21</v>
       </c>
@@ -2466,9 +2358,6 @@
       <c r="E40" t="s">
         <v>20</v>
       </c>
-      <c r="F40">
-        <v>2001</v>
-      </c>
       <c r="G40" t="s">
         <v>21</v>
       </c>
@@ -2516,9 +2405,6 @@
       <c r="E41" t="s">
         <v>20</v>
       </c>
-      <c r="F41">
-        <v>2001</v>
-      </c>
       <c r="G41" t="s">
         <v>21</v>
       </c>
@@ -2566,9 +2452,6 @@
       <c r="E42" t="s">
         <v>20</v>
       </c>
-      <c r="F42">
-        <v>2001</v>
-      </c>
       <c r="G42" t="s">
         <v>21</v>
       </c>
@@ -2616,9 +2499,6 @@
       <c r="E43" t="s">
         <v>20</v>
       </c>
-      <c r="F43">
-        <v>2001</v>
-      </c>
       <c r="G43" t="s">
         <v>21</v>
       </c>
@@ -2666,9 +2546,6 @@
       <c r="E44" t="s">
         <v>20</v>
       </c>
-      <c r="F44">
-        <v>2001</v>
-      </c>
       <c r="G44" t="s">
         <v>21</v>
       </c>
@@ -2716,9 +2593,6 @@
       <c r="E45" t="s">
         <v>20</v>
       </c>
-      <c r="F45">
-        <v>2001</v>
-      </c>
       <c r="G45" t="s">
         <v>21</v>
       </c>
@@ -2766,9 +2640,6 @@
       <c r="E46" t="s">
         <v>20</v>
       </c>
-      <c r="F46">
-        <v>2001</v>
-      </c>
       <c r="G46" t="s">
         <v>21</v>
       </c>
@@ -2816,9 +2687,6 @@
       <c r="E47" t="s">
         <v>20</v>
       </c>
-      <c r="F47">
-        <v>2001</v>
-      </c>
       <c r="G47" t="s">
         <v>21</v>
       </c>
@@ -2866,9 +2734,6 @@
       <c r="E48" t="s">
         <v>20</v>
       </c>
-      <c r="F48">
-        <v>2001</v>
-      </c>
       <c r="G48" t="s">
         <v>21</v>
       </c>
@@ -2916,9 +2781,6 @@
       <c r="E49" t="s">
         <v>20</v>
       </c>
-      <c r="F49">
-        <v>2001</v>
-      </c>
       <c r="G49" t="s">
         <v>21</v>
       </c>
@@ -2966,9 +2828,6 @@
       <c r="E50" t="s">
         <v>20</v>
       </c>
-      <c r="F50">
-        <v>2001</v>
-      </c>
       <c r="G50" t="s">
         <v>21</v>
       </c>
@@ -3016,9 +2875,6 @@
       <c r="E51" t="s">
         <v>20</v>
       </c>
-      <c r="F51">
-        <v>2001</v>
-      </c>
       <c r="G51" t="s">
         <v>21</v>
       </c>
@@ -3066,9 +2922,6 @@
       <c r="E52" t="s">
         <v>20</v>
       </c>
-      <c r="F52">
-        <v>2001</v>
-      </c>
       <c r="G52" t="s">
         <v>21</v>
       </c>
@@ -3116,9 +2969,6 @@
       <c r="E53" t="s">
         <v>20</v>
       </c>
-      <c r="F53">
-        <v>2001</v>
-      </c>
       <c r="G53" t="s">
         <v>21</v>
       </c>
@@ -3166,9 +3016,6 @@
       <c r="E54" t="s">
         <v>20</v>
       </c>
-      <c r="F54">
-        <v>2001</v>
-      </c>
       <c r="G54" t="s">
         <v>21</v>
       </c>
@@ -3216,9 +3063,6 @@
       <c r="E55" t="s">
         <v>20</v>
       </c>
-      <c r="F55">
-        <v>2001</v>
-      </c>
       <c r="G55" t="s">
         <v>21</v>
       </c>
@@ -3266,9 +3110,6 @@
       <c r="E56" t="s">
         <v>20</v>
       </c>
-      <c r="F56">
-        <v>2001</v>
-      </c>
       <c r="G56" t="s">
         <v>21</v>
       </c>
@@ -3316,9 +3157,6 @@
       <c r="E57" t="s">
         <v>20</v>
       </c>
-      <c r="F57">
-        <v>2001</v>
-      </c>
       <c r="G57" t="s">
         <v>21</v>
       </c>
@@ -3366,9 +3204,6 @@
       <c r="E58" t="s">
         <v>20</v>
       </c>
-      <c r="F58">
-        <v>2001</v>
-      </c>
       <c r="G58" t="s">
         <v>21</v>
       </c>
@@ -3416,9 +3251,6 @@
       <c r="E59" t="s">
         <v>20</v>
       </c>
-      <c r="F59">
-        <v>2001</v>
-      </c>
       <c r="G59" t="s">
         <v>21</v>
       </c>
@@ -3466,9 +3298,6 @@
       <c r="E60" t="s">
         <v>20</v>
       </c>
-      <c r="F60">
-        <v>2001</v>
-      </c>
       <c r="G60" t="s">
         <v>21</v>
       </c>
@@ -3516,9 +3345,6 @@
       <c r="E61" t="s">
         <v>20</v>
       </c>
-      <c r="F61">
-        <v>2001</v>
-      </c>
       <c r="G61" t="s">
         <v>21</v>
       </c>
@@ -3566,9 +3392,6 @@
       <c r="E62" t="s">
         <v>20</v>
       </c>
-      <c r="F62">
-        <v>2001</v>
-      </c>
       <c r="G62" t="s">
         <v>21</v>
       </c>
@@ -3616,9 +3439,6 @@
       <c r="E63" t="s">
         <v>20</v>
       </c>
-      <c r="F63">
-        <v>2001</v>
-      </c>
       <c r="G63" t="s">
         <v>21</v>
       </c>
@@ -3666,9 +3486,6 @@
       <c r="E64" t="s">
         <v>20</v>
       </c>
-      <c r="F64">
-        <v>2001</v>
-      </c>
       <c r="G64" t="s">
         <v>21</v>
       </c>
@@ -3716,9 +3533,6 @@
       <c r="E65" t="s">
         <v>20</v>
       </c>
-      <c r="F65">
-        <v>2001</v>
-      </c>
       <c r="G65" t="s">
         <v>21</v>
       </c>
@@ -3766,9 +3580,6 @@
       <c r="E66" t="s">
         <v>20</v>
       </c>
-      <c r="F66">
-        <v>2001</v>
-      </c>
       <c r="G66" t="s">
         <v>21</v>
       </c>
@@ -3816,9 +3627,6 @@
       <c r="E67" t="s">
         <v>20</v>
       </c>
-      <c r="F67">
-        <v>2001</v>
-      </c>
       <c r="G67" t="s">
         <v>21</v>
       </c>
@@ -3866,9 +3674,6 @@
       <c r="E68" t="s">
         <v>20</v>
       </c>
-      <c r="F68">
-        <v>2001</v>
-      </c>
       <c r="G68" t="s">
         <v>21</v>
       </c>
@@ -3916,9 +3721,6 @@
       <c r="E69" t="s">
         <v>20</v>
       </c>
-      <c r="F69">
-        <v>2001</v>
-      </c>
       <c r="G69" t="s">
         <v>21</v>
       </c>
@@ -3966,9 +3768,6 @@
       <c r="E70" t="s">
         <v>20</v>
       </c>
-      <c r="F70">
-        <v>2001</v>
-      </c>
       <c r="G70" t="s">
         <v>21</v>
       </c>
@@ -4016,9 +3815,6 @@
       <c r="E71" t="s">
         <v>20</v>
       </c>
-      <c r="F71">
-        <v>2001</v>
-      </c>
       <c r="G71" t="s">
         <v>21</v>
       </c>
@@ -4066,9 +3862,6 @@
       <c r="E72" t="s">
         <v>20</v>
       </c>
-      <c r="F72">
-        <v>2001</v>
-      </c>
       <c r="G72" t="s">
         <v>21</v>
       </c>
@@ -4116,9 +3909,6 @@
       <c r="E73" t="s">
         <v>20</v>
       </c>
-      <c r="F73">
-        <v>2001</v>
-      </c>
       <c r="G73" t="s">
         <v>21</v>
       </c>
@@ -4166,9 +3956,6 @@
       <c r="E74" t="s">
         <v>20</v>
       </c>
-      <c r="F74">
-        <v>2001</v>
-      </c>
       <c r="G74" t="s">
         <v>21</v>
       </c>
@@ -4216,9 +4003,6 @@
       <c r="E75" t="s">
         <v>20</v>
       </c>
-      <c r="F75">
-        <v>2001</v>
-      </c>
       <c r="G75" t="s">
         <v>21</v>
       </c>
@@ -4266,9 +4050,6 @@
       <c r="E76" t="s">
         <v>20</v>
       </c>
-      <c r="F76">
-        <v>2001</v>
-      </c>
       <c r="G76" t="s">
         <v>21</v>
       </c>
@@ -4316,9 +4097,6 @@
       <c r="E77" t="s">
         <v>20</v>
       </c>
-      <c r="F77">
-        <v>2001</v>
-      </c>
       <c r="G77" t="s">
         <v>21</v>
       </c>
@@ -4366,9 +4144,6 @@
       <c r="E78" t="s">
         <v>20</v>
       </c>
-      <c r="F78">
-        <v>2001</v>
-      </c>
       <c r="G78" t="s">
         <v>21</v>
       </c>
@@ -4416,9 +4191,6 @@
       <c r="E79" t="s">
         <v>20</v>
       </c>
-      <c r="F79">
-        <v>2001</v>
-      </c>
       <c r="G79" t="s">
         <v>21</v>
       </c>
@@ -4466,9 +4238,6 @@
       <c r="E80" t="s">
         <v>20</v>
       </c>
-      <c r="F80">
-        <v>2001</v>
-      </c>
       <c r="G80" t="s">
         <v>21</v>
       </c>
@@ -4516,9 +4285,6 @@
       <c r="E81" t="s">
         <v>20</v>
       </c>
-      <c r="F81">
-        <v>2001</v>
-      </c>
       <c r="G81" t="s">
         <v>21</v>
       </c>
@@ -4566,9 +4332,6 @@
       <c r="E82" t="s">
         <v>20</v>
       </c>
-      <c r="F82">
-        <v>2001</v>
-      </c>
       <c r="G82" t="s">
         <v>21</v>
       </c>
@@ -4616,9 +4379,6 @@
       <c r="E83" t="s">
         <v>20</v>
       </c>
-      <c r="F83">
-        <v>2001</v>
-      </c>
       <c r="G83" t="s">
         <v>21</v>
       </c>
@@ -4666,9 +4426,6 @@
       <c r="E84" t="s">
         <v>20</v>
       </c>
-      <c r="F84">
-        <v>2001</v>
-      </c>
       <c r="G84" t="s">
         <v>21</v>
       </c>
@@ -4716,9 +4473,6 @@
       <c r="E85" t="s">
         <v>20</v>
       </c>
-      <c r="F85">
-        <v>2001</v>
-      </c>
       <c r="G85" t="s">
         <v>21</v>
       </c>
@@ -4766,9 +4520,6 @@
       <c r="E86" t="s">
         <v>20</v>
       </c>
-      <c r="F86">
-        <v>2001</v>
-      </c>
       <c r="G86" t="s">
         <v>21</v>
       </c>
@@ -4816,9 +4567,6 @@
       <c r="E87" t="s">
         <v>20</v>
       </c>
-      <c r="F87">
-        <v>2001</v>
-      </c>
       <c r="G87" t="s">
         <v>21</v>
       </c>
@@ -4866,9 +4614,6 @@
       <c r="E88" t="s">
         <v>20</v>
       </c>
-      <c r="F88">
-        <v>2001</v>
-      </c>
       <c r="G88" t="s">
         <v>21</v>
       </c>
@@ -4916,9 +4661,6 @@
       <c r="E89" t="s">
         <v>20</v>
       </c>
-      <c r="F89">
-        <v>2001</v>
-      </c>
       <c r="G89" t="s">
         <v>21</v>
       </c>
@@ -4966,9 +4708,6 @@
       <c r="E90" t="s">
         <v>20</v>
       </c>
-      <c r="F90">
-        <v>2001</v>
-      </c>
       <c r="G90" t="s">
         <v>21</v>
       </c>
@@ -5016,9 +4755,6 @@
       <c r="E91" t="s">
         <v>20</v>
       </c>
-      <c r="F91">
-        <v>2001</v>
-      </c>
       <c r="G91" t="s">
         <v>21</v>
       </c>
@@ -5066,9 +4802,6 @@
       <c r="E92" t="s">
         <v>20</v>
       </c>
-      <c r="F92">
-        <v>2001</v>
-      </c>
       <c r="G92" t="s">
         <v>21</v>
       </c>
@@ -5116,9 +4849,6 @@
       <c r="E93" t="s">
         <v>20</v>
       </c>
-      <c r="F93">
-        <v>2001</v>
-      </c>
       <c r="G93" t="s">
         <v>21</v>
       </c>
@@ -5166,9 +4896,6 @@
       <c r="E94" t="s">
         <v>20</v>
       </c>
-      <c r="F94">
-        <v>2001</v>
-      </c>
       <c r="G94" t="s">
         <v>21</v>
       </c>
@@ -5216,9 +4943,6 @@
       <c r="E95" t="s">
         <v>20</v>
       </c>
-      <c r="F95">
-        <v>2001</v>
-      </c>
       <c r="G95" t="s">
         <v>21</v>
       </c>
@@ -5266,9 +4990,6 @@
       <c r="E96" t="s">
         <v>20</v>
       </c>
-      <c r="F96">
-        <v>2001</v>
-      </c>
       <c r="G96" t="s">
         <v>21</v>
       </c>
@@ -5316,9 +5037,6 @@
       <c r="E97" t="s">
         <v>20</v>
       </c>
-      <c r="F97">
-        <v>2001</v>
-      </c>
       <c r="G97" t="s">
         <v>21</v>
       </c>
@@ -5366,9 +5084,6 @@
       <c r="E98" t="s">
         <v>20</v>
       </c>
-      <c r="F98">
-        <v>2001</v>
-      </c>
       <c r="G98" t="s">
         <v>21</v>
       </c>
@@ -5416,9 +5131,6 @@
       <c r="E99" t="s">
         <v>20</v>
       </c>
-      <c r="F99">
-        <v>2001</v>
-      </c>
       <c r="G99" t="s">
         <v>21</v>
       </c>
@@ -5466,9 +5178,6 @@
       <c r="E100" t="s">
         <v>20</v>
       </c>
-      <c r="F100">
-        <v>2001</v>
-      </c>
       <c r="G100" t="s">
         <v>21</v>
       </c>
@@ -5516,9 +5225,6 @@
       <c r="E101" t="s">
         <v>20</v>
       </c>
-      <c r="F101">
-        <v>2001</v>
-      </c>
       <c r="G101" t="s">
         <v>21</v>
       </c>
@@ -5566,9 +5272,6 @@
       <c r="E102" t="s">
         <v>20</v>
       </c>
-      <c r="F102">
-        <v>2001</v>
-      </c>
       <c r="G102" t="s">
         <v>21</v>
       </c>
@@ -5616,9 +5319,6 @@
       <c r="E103" t="s">
         <v>20</v>
       </c>
-      <c r="F103">
-        <v>2001</v>
-      </c>
       <c r="G103" t="s">
         <v>21</v>
       </c>
@@ -5666,9 +5366,6 @@
       <c r="E104" t="s">
         <v>20</v>
       </c>
-      <c r="F104">
-        <v>2001</v>
-      </c>
       <c r="G104" t="s">
         <v>21</v>
       </c>
@@ -5716,9 +5413,6 @@
       <c r="E105" t="s">
         <v>20</v>
       </c>
-      <c r="F105">
-        <v>2001</v>
-      </c>
       <c r="G105" t="s">
         <v>21</v>
       </c>
@@ -5766,9 +5460,6 @@
       <c r="E106" t="s">
         <v>20</v>
       </c>
-      <c r="F106">
-        <v>2001</v>
-      </c>
       <c r="G106" t="s">
         <v>21</v>
       </c>
@@ -5816,9 +5507,6 @@
       <c r="E107" t="s">
         <v>20</v>
       </c>
-      <c r="F107">
-        <v>2001</v>
-      </c>
       <c r="G107" t="s">
         <v>21</v>
       </c>
@@ -5866,9 +5554,6 @@
       <c r="E108" t="s">
         <v>20</v>
       </c>
-      <c r="F108">
-        <v>2001</v>
-      </c>
       <c r="G108" t="s">
         <v>21</v>
       </c>
@@ -5916,9 +5601,6 @@
       <c r="E109" t="s">
         <v>20</v>
       </c>
-      <c r="F109">
-        <v>2001</v>
-      </c>
       <c r="G109" t="s">
         <v>21</v>
       </c>
@@ -5966,9 +5648,6 @@
       <c r="E110" t="s">
         <v>20</v>
       </c>
-      <c r="F110">
-        <v>2001</v>
-      </c>
       <c r="G110" t="s">
         <v>21</v>
       </c>
@@ -6016,9 +5695,6 @@
       <c r="E111" t="s">
         <v>20</v>
       </c>
-      <c r="F111">
-        <v>2001</v>
-      </c>
       <c r="G111" t="s">
         <v>21</v>
       </c>
@@ -6066,9 +5742,6 @@
       <c r="E112" t="s">
         <v>20</v>
       </c>
-      <c r="F112">
-        <v>2001</v>
-      </c>
       <c r="G112" t="s">
         <v>21</v>
       </c>
@@ -6116,9 +5789,6 @@
       <c r="E113" t="s">
         <v>20</v>
       </c>
-      <c r="F113">
-        <v>2001</v>
-      </c>
       <c r="G113" t="s">
         <v>21</v>
       </c>
@@ -6166,9 +5836,6 @@
       <c r="E114" t="s">
         <v>20</v>
       </c>
-      <c r="F114">
-        <v>2001</v>
-      </c>
       <c r="G114" t="s">
         <v>21</v>
       </c>
@@ -6216,9 +5883,6 @@
       <c r="E115" t="s">
         <v>20</v>
       </c>
-      <c r="F115">
-        <v>2001</v>
-      </c>
       <c r="G115" t="s">
         <v>21</v>
       </c>
@@ -6266,9 +5930,6 @@
       <c r="E116" t="s">
         <v>20</v>
       </c>
-      <c r="F116">
-        <v>2001</v>
-      </c>
       <c r="G116" t="s">
         <v>21</v>
       </c>
@@ -6316,9 +5977,6 @@
       <c r="E117" t="s">
         <v>20</v>
       </c>
-      <c r="F117">
-        <v>2001</v>
-      </c>
       <c r="G117" t="s">
         <v>21</v>
       </c>
@@ -6366,9 +6024,6 @@
       <c r="E118" t="s">
         <v>20</v>
       </c>
-      <c r="F118">
-        <v>2001</v>
-      </c>
       <c r="G118" t="s">
         <v>21</v>
       </c>
@@ -6416,9 +6071,6 @@
       <c r="E119" t="s">
         <v>20</v>
       </c>
-      <c r="F119">
-        <v>2001</v>
-      </c>
       <c r="G119" t="s">
         <v>21</v>
       </c>
@@ -6466,9 +6118,6 @@
       <c r="E120" t="s">
         <v>20</v>
       </c>
-      <c r="F120">
-        <v>2001</v>
-      </c>
       <c r="G120" t="s">
         <v>21</v>
       </c>
@@ -6516,9 +6165,6 @@
       <c r="E121" t="s">
         <v>20</v>
       </c>
-      <c r="F121">
-        <v>2001</v>
-      </c>
       <c r="G121" t="s">
         <v>21</v>
       </c>
@@ -6566,9 +6212,6 @@
       <c r="E122" t="s">
         <v>20</v>
       </c>
-      <c r="F122">
-        <v>2001</v>
-      </c>
       <c r="G122" t="s">
         <v>21</v>
       </c>
@@ -6616,9 +6259,6 @@
       <c r="E123" t="s">
         <v>20</v>
       </c>
-      <c r="F123">
-        <v>2001</v>
-      </c>
       <c r="G123" t="s">
         <v>21</v>
       </c>
@@ -6666,9 +6306,6 @@
       <c r="E124" t="s">
         <v>20</v>
       </c>
-      <c r="F124">
-        <v>2001</v>
-      </c>
       <c r="G124" t="s">
         <v>21</v>
       </c>
@@ -6716,9 +6353,6 @@
       <c r="E125" t="s">
         <v>20</v>
       </c>
-      <c r="F125">
-        <v>2001</v>
-      </c>
       <c r="G125" t="s">
         <v>21</v>
       </c>
@@ -6766,9 +6400,6 @@
       <c r="E126" t="s">
         <v>20</v>
       </c>
-      <c r="F126">
-        <v>2001</v>
-      </c>
       <c r="G126" t="s">
         <v>21</v>
       </c>
@@ -6816,9 +6447,6 @@
       <c r="E127" t="s">
         <v>20</v>
       </c>
-      <c r="F127">
-        <v>2001</v>
-      </c>
       <c r="G127" t="s">
         <v>21</v>
       </c>
@@ -6866,9 +6494,6 @@
       <c r="E128" t="s">
         <v>20</v>
       </c>
-      <c r="F128">
-        <v>2001</v>
-      </c>
       <c r="G128" t="s">
         <v>21</v>
       </c>
@@ -6916,9 +6541,6 @@
       <c r="E129" t="s">
         <v>20</v>
       </c>
-      <c r="F129">
-        <v>2001</v>
-      </c>
       <c r="G129" t="s">
         <v>21</v>
       </c>
@@ -6966,9 +6588,6 @@
       <c r="E130" t="s">
         <v>20</v>
       </c>
-      <c r="F130">
-        <v>2001</v>
-      </c>
       <c r="G130" t="s">
         <v>21</v>
       </c>
@@ -7016,9 +6635,6 @@
       <c r="E131" t="s">
         <v>20</v>
       </c>
-      <c r="F131">
-        <v>2001</v>
-      </c>
       <c r="G131" t="s">
         <v>21</v>
       </c>
@@ -7066,9 +6682,6 @@
       <c r="E132" t="s">
         <v>20</v>
       </c>
-      <c r="F132">
-        <v>2001</v>
-      </c>
       <c r="G132" t="s">
         <v>21</v>
       </c>
@@ -7116,9 +6729,6 @@
       <c r="E133" t="s">
         <v>20</v>
       </c>
-      <c r="F133">
-        <v>2001</v>
-      </c>
       <c r="G133" t="s">
         <v>21</v>
       </c>
@@ -7166,9 +6776,6 @@
       <c r="E134" t="s">
         <v>20</v>
       </c>
-      <c r="F134">
-        <v>2001</v>
-      </c>
       <c r="G134" t="s">
         <v>21</v>
       </c>
@@ -7216,9 +6823,6 @@
       <c r="E135" t="s">
         <v>20</v>
       </c>
-      <c r="F135">
-        <v>2001</v>
-      </c>
       <c r="G135" t="s">
         <v>21</v>
       </c>
@@ -7266,9 +6870,6 @@
       <c r="E136" t="s">
         <v>20</v>
       </c>
-      <c r="F136">
-        <v>2001</v>
-      </c>
       <c r="G136" t="s">
         <v>21</v>
       </c>
@@ -7316,9 +6917,6 @@
       <c r="E137" t="s">
         <v>20</v>
       </c>
-      <c r="F137">
-        <v>2001</v>
-      </c>
       <c r="G137" t="s">
         <v>21</v>
       </c>
@@ -7366,9 +6964,6 @@
       <c r="E138" t="s">
         <v>20</v>
       </c>
-      <c r="F138">
-        <v>2001</v>
-      </c>
       <c r="G138" t="s">
         <v>21</v>
       </c>
@@ -7416,9 +7011,6 @@
       <c r="E139" t="s">
         <v>20</v>
       </c>
-      <c r="F139">
-        <v>2001</v>
-      </c>
       <c r="G139" t="s">
         <v>21</v>
       </c>
@@ -7466,9 +7058,6 @@
       <c r="E140" t="s">
         <v>20</v>
       </c>
-      <c r="F140">
-        <v>2001</v>
-      </c>
       <c r="G140" t="s">
         <v>21</v>
       </c>
@@ -7516,9 +7105,6 @@
       <c r="E141" t="s">
         <v>20</v>
       </c>
-      <c r="F141">
-        <v>2001</v>
-      </c>
       <c r="G141" t="s">
         <v>21</v>
       </c>
@@ -7566,9 +7152,6 @@
       <c r="E142" t="s">
         <v>20</v>
       </c>
-      <c r="F142">
-        <v>2001</v>
-      </c>
       <c r="G142" t="s">
         <v>21</v>
       </c>
@@ -7616,9 +7199,6 @@
       <c r="E143" t="s">
         <v>20</v>
       </c>
-      <c r="F143">
-        <v>2001</v>
-      </c>
       <c r="G143" t="s">
         <v>21</v>
       </c>
@@ -7666,9 +7246,6 @@
       <c r="E144" t="s">
         <v>20</v>
       </c>
-      <c r="F144">
-        <v>2001</v>
-      </c>
       <c r="G144" t="s">
         <v>21</v>
       </c>
@@ -7716,9 +7293,6 @@
       <c r="E145" t="s">
         <v>20</v>
       </c>
-      <c r="F145">
-        <v>2001</v>
-      </c>
       <c r="G145" t="s">
         <v>21</v>
       </c>
@@ -7766,9 +7340,6 @@
       <c r="E146" t="s">
         <v>20</v>
       </c>
-      <c r="F146">
-        <v>2001</v>
-      </c>
       <c r="G146" t="s">
         <v>21</v>
       </c>
@@ -7816,9 +7387,6 @@
       <c r="E147" t="s">
         <v>20</v>
       </c>
-      <c r="F147">
-        <v>2001</v>
-      </c>
       <c r="G147" t="s">
         <v>21</v>
       </c>
@@ -7866,9 +7434,6 @@
       <c r="E148" t="s">
         <v>20</v>
       </c>
-      <c r="F148">
-        <v>2001</v>
-      </c>
       <c r="G148" t="s">
         <v>21</v>
       </c>
@@ -7916,9 +7481,6 @@
       <c r="E149" t="s">
         <v>20</v>
       </c>
-      <c r="F149">
-        <v>2001</v>
-      </c>
       <c r="G149" t="s">
         <v>21</v>
       </c>
@@ -7966,9 +7528,6 @@
       <c r="E150" t="s">
         <v>20</v>
       </c>
-      <c r="F150">
-        <v>2001</v>
-      </c>
       <c r="G150" t="s">
         <v>21</v>
       </c>
@@ -8016,9 +7575,6 @@
       <c r="E151" t="s">
         <v>20</v>
       </c>
-      <c r="F151">
-        <v>2001</v>
-      </c>
       <c r="G151" t="s">
         <v>21</v>
       </c>
@@ -8066,9 +7622,6 @@
       <c r="E152" t="s">
         <v>20</v>
       </c>
-      <c r="F152">
-        <v>2001</v>
-      </c>
       <c r="G152" t="s">
         <v>21</v>
       </c>
@@ -8116,9 +7669,6 @@
       <c r="E153" t="s">
         <v>20</v>
       </c>
-      <c r="F153">
-        <v>2001</v>
-      </c>
       <c r="G153" t="s">
         <v>21</v>
       </c>
@@ -8166,9 +7716,6 @@
       <c r="E154" t="s">
         <v>20</v>
       </c>
-      <c r="F154">
-        <v>2001</v>
-      </c>
       <c r="G154" t="s">
         <v>21</v>
       </c>
@@ -8216,9 +7763,6 @@
       <c r="E155" t="s">
         <v>20</v>
       </c>
-      <c r="F155">
-        <v>2001</v>
-      </c>
       <c r="G155" t="s">
         <v>21</v>
       </c>
@@ -8266,9 +7810,6 @@
       <c r="E156" t="s">
         <v>20</v>
       </c>
-      <c r="F156">
-        <v>2001</v>
-      </c>
       <c r="G156" t="s">
         <v>21</v>
       </c>
@@ -8316,9 +7857,6 @@
       <c r="E157" t="s">
         <v>20</v>
       </c>
-      <c r="F157">
-        <v>2001</v>
-      </c>
       <c r="G157" t="s">
         <v>21</v>
       </c>
@@ -8366,9 +7904,6 @@
       <c r="E158" t="s">
         <v>20</v>
       </c>
-      <c r="F158">
-        <v>2001</v>
-      </c>
       <c r="G158" t="s">
         <v>21</v>
       </c>
@@ -8416,9 +7951,6 @@
       <c r="E159" t="s">
         <v>20</v>
       </c>
-      <c r="F159">
-        <v>2001</v>
-      </c>
       <c r="G159" t="s">
         <v>21</v>
       </c>
@@ -8466,9 +7998,6 @@
       <c r="E160" t="s">
         <v>20</v>
       </c>
-      <c r="F160">
-        <v>2001</v>
-      </c>
       <c r="G160" t="s">
         <v>21</v>
       </c>
@@ -8516,9 +8045,6 @@
       <c r="E161" t="s">
         <v>20</v>
       </c>
-      <c r="F161">
-        <v>2001</v>
-      </c>
       <c r="G161" t="s">
         <v>21</v>
       </c>
@@ -8566,9 +8092,6 @@
       <c r="E162" t="s">
         <v>20</v>
       </c>
-      <c r="F162">
-        <v>2001</v>
-      </c>
       <c r="G162" t="s">
         <v>21</v>
       </c>
@@ -8616,9 +8139,6 @@
       <c r="E163" t="s">
         <v>20</v>
       </c>
-      <c r="F163">
-        <v>2001</v>
-      </c>
       <c r="G163" t="s">
         <v>21</v>
       </c>
@@ -8666,9 +8186,6 @@
       <c r="E164" t="s">
         <v>20</v>
       </c>
-      <c r="F164">
-        <v>2001</v>
-      </c>
       <c r="G164" t="s">
         <v>21</v>
       </c>
@@ -8715,9 +8232,6 @@
       </c>
       <c r="E165" t="s">
         <v>20</v>
-      </c>
-      <c r="F165">
-        <v>2001</v>
       </c>
       <c r="G165" t="s">
         <v>21</v>
